--- a/prep_and_checklists/ShopMy  /PREPLIST_ShopMy  _03-10-2026_0.xlsx
+++ b/prep_and_checklists/ShopMy  /PREPLIST_ShopMy  _03-10-2026_0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/ShopMy  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC661A6-B1A8-AB47-89DA-7E57ECC5E2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301B6340-211E-7748-99E6-EF69BB64FB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prep_sheet" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="96">
   <si>
     <t xml:space="preserve">ShopMy  , Guests: 65   , 5:30 PM - 7:30 PM   ,Monday, March 23, 2026  </t>
   </si>
@@ -41,9 +41,6 @@
     <t>cut mini hotdog buns</t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
     <t>make lobster salad kit</t>
   </si>
   <si>
@@ -270,6 +267,48 @@
   </si>
   <si>
     <t>5:30-6pm, 7-7:30pm PASSED CANAPES</t>
+  </si>
+  <si>
+    <t>120 pcs</t>
+  </si>
+  <si>
+    <t>1 x recipe</t>
+  </si>
+  <si>
+    <t>1 cup</t>
+  </si>
+  <si>
+    <t>2lbs</t>
+  </si>
+  <si>
+    <t>1x 200g tin</t>
+  </si>
+  <si>
+    <t>1 x recipe, in a piping bag</t>
+  </si>
+  <si>
+    <t>1x cup, pull from reach-in freezer</t>
+  </si>
+  <si>
+    <t>1 x cup, pull from reach-in freezer</t>
+  </si>
+  <si>
+    <t>1x piping bag</t>
+  </si>
+  <si>
+    <t>3 pcs</t>
+  </si>
+  <si>
+    <t>1 cup, pull from reach-in</t>
+  </si>
+  <si>
+    <t>1 x squeeze bottle</t>
+  </si>
+  <si>
+    <t>1 pack</t>
+  </si>
+  <si>
+    <t>1 quart, in a piping bag</t>
   </si>
 </sst>
 </file>
@@ -415,16 +454,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -727,11 +766,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.1640625" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.25">
@@ -745,16 +787,16 @@
       </c>
     </row>
     <row r="4" spans="1:2" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="8"/>
+      <c r="B4" s="10"/>
     </row>
     <row r="5" spans="1:2" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" s="10"/>
+      <c r="A5" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="8"/>
     </row>
     <row r="6" spans="1:2" ht="19" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -769,36 +811,36 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>6</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="19" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>4</v>
@@ -806,39 +848,39 @@
     </row>
     <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>6</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="19" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>4</v>
@@ -846,39 +888,39 @@
     </row>
     <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>6</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="19" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>4</v>
@@ -886,47 +928,47 @@
     </row>
     <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>6</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>6</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="19" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>4</v>
@@ -934,31 +976,31 @@
     </row>
     <row r="32" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="19" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>4</v>
@@ -966,34 +1008,34 @@
     </row>
     <row r="37" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>6</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>6</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1002,7 +1044,7 @@
     <mergeCell ref="A4:B4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup scale="90" orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -1013,7 +1055,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="19" x14ac:dyDescent="0.2">
@@ -1023,331 +1065,332 @@
     </row>
     <row r="3" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>